--- a/CYP3A5/CYP3A5_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A5/CYP3A5_Allele_def_rs_excluidos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP3A5\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,13 +64,13 @@
     <t>Base  de datos</t>
   </si>
   <si>
-    <t xml:space="preserve">ClinPGX </t>
-  </si>
-  <si>
-    <t>CYP3A5_frequency_table</t>
-  </si>
-  <si>
     <t xml:space="preserve">rs/*alelo </t>
+  </si>
+  <si>
+    <t>dbSNP</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs41303343</t>
   </si>
 </sst>
 </file>
@@ -94,7 +94,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +104,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -120,12 +126,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,13 +499,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="5" width="25.5703125" customWidth="1"/>
+    <col min="3" max="4" width="25.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,21 +518,22 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -528,7 +541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -541,18 +554,22 @@
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
+      <c r="E4">
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C5">
         <f>SUM(C4)</f>
         <v>0</v>
       </c>
+      <c r="E5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
